--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -2686,65 +2686,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129482344</v>
+        <v>129481322</v>
       </c>
       <c r="B20" t="n">
-        <v>56917</v>
+        <v>96016</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477243</v>
+        <v>477368</v>
       </c>
       <c r="R20" t="n">
-        <v>6592288</v>
+        <v>6592070</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129481322</v>
+        <v>129492837</v>
       </c>
       <c r="B21" t="n">
-        <v>96016</v>
+        <v>97401</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,21 +2804,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477368</v>
+        <v>477205</v>
       </c>
       <c r="R21" t="n">
-        <v>6592070</v>
+        <v>6592083</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,7 +2863,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2873,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,45 +2900,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129492837</v>
+        <v>129482344</v>
       </c>
       <c r="B22" t="n">
-        <v>97401</v>
+        <v>56917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2569</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477205</v>
+        <v>477243</v>
       </c>
       <c r="R22" t="n">
-        <v>6592083</v>
+        <v>6592288</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2686,45 +2686,65 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129481322</v>
+        <v>129482344</v>
       </c>
       <c r="B20" t="n">
-        <v>96016</v>
+        <v>56917</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477368</v>
+        <v>477243</v>
       </c>
       <c r="R20" t="n">
-        <v>6592070</v>
+        <v>6592288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129492837</v>
+        <v>129481322</v>
       </c>
       <c r="B21" t="n">
-        <v>97401</v>
+        <v>96026</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2804,21 +2824,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2828,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477205</v>
+        <v>477368</v>
       </c>
       <c r="R21" t="n">
-        <v>6592083</v>
+        <v>6592070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2863,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2873,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,65 +2920,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129482344</v>
+        <v>129492837</v>
       </c>
       <c r="B22" t="n">
-        <v>56917</v>
+        <v>97411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>2569</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477243</v>
+        <v>477205</v>
       </c>
       <c r="R22" t="n">
-        <v>6592288</v>
+        <v>6592083</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3134,59 +3134,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129481249</v>
+        <v>129481787</v>
       </c>
       <c r="B24" t="n">
-        <v>57896</v>
+        <v>97411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>2569</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477378</v>
+        <v>477295</v>
       </c>
       <c r="R24" t="n">
-        <v>6592070</v>
+        <v>6592173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3218,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,7 +3214,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,45 +3241,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129481787</v>
+        <v>129481249</v>
       </c>
       <c r="B25" t="n">
-        <v>97401</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477295</v>
+        <v>477378</v>
       </c>
       <c r="R25" t="n">
-        <v>6592173</v>
+        <v>6592070</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3359,6 +3359,220 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129926849</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>477266</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6592122</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129927635</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>477326</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6592004</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3365,7 +3365,7 @@
         <v>129926849</v>
       </c>
       <c r="B26" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129927635</v>
       </c>
       <c r="B27" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3365,7 +3365,7 @@
         <v>129926849</v>
       </c>
       <c r="B26" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129927635</v>
       </c>
       <c r="B27" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3365,7 +3365,7 @@
         <v>129926849</v>
       </c>
       <c r="B26" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129927635</v>
       </c>
       <c r="B27" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3365,7 +3365,7 @@
         <v>129926849</v>
       </c>
       <c r="B26" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129927635</v>
       </c>
       <c r="B27" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3574,6 +3574,112 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130210236</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Karlsdal, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>477221</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6592064</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3472,7 +3472,7 @@
         <v>129927635</v>
       </c>
       <c r="B27" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3365,7 +3365,7 @@
         <v>129926849</v>
       </c>
       <c r="B26" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>129927635</v>
       </c>
       <c r="B27" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>130210236</v>
       </c>
       <c r="B28" t="n">
-        <v>97454</v>
+        <v>97541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3579,7 +3579,7 @@
         <v>130210236</v>
       </c>
       <c r="B28" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3579,7 +3579,7 @@
         <v>130210236</v>
       </c>
       <c r="B28" t="n">
-        <v>97544</v>
+        <v>97570</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3579,7 +3579,7 @@
         <v>130210236</v>
       </c>
       <c r="B28" t="n">
-        <v>97570</v>
+        <v>97571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3579,7 +3579,7 @@
         <v>130210236</v>
       </c>
       <c r="B28" t="n">
-        <v>97571</v>
+        <v>97572</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3579,7 +3579,7 @@
         <v>130210236</v>
       </c>
       <c r="B28" t="n">
-        <v>97572</v>
+        <v>97574</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3579,7 +3579,7 @@
         <v>130210236</v>
       </c>
       <c r="B28" t="n">
-        <v>97574</v>
+        <v>97578</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3685,7 +3685,7 @@
         <v>131114362</v>
       </c>
       <c r="B29" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3685,7 +3685,7 @@
         <v>131114362</v>
       </c>
       <c r="B29" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3787,6 +3787,362 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131333328</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>477310</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6592199</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131333420</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91776</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>477285</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6592033</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131334799</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>477212</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6592292</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Grop i snötäcket.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3685,7 +3685,7 @@
         <v>131114362</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>131333420</v>
       </c>
       <c r="B31" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3685,7 +3685,7 @@
         <v>131114362</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>131333328</v>
       </c>
       <c r="B30" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>131333420</v>
       </c>
       <c r="B31" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>131334799</v>
       </c>
       <c r="B32" t="n">
-        <v>57076</v>
+        <v>57078</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3685,7 +3685,7 @@
         <v>131114362</v>
       </c>
       <c r="B29" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>131333328</v>
       </c>
       <c r="B30" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>131333420</v>
       </c>
       <c r="B31" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>131334799</v>
       </c>
       <c r="B32" t="n">
-        <v>57078</v>
+        <v>57079</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -3685,7 +3685,7 @@
         <v>131114362</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>131333328</v>
       </c>
       <c r="B30" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>131333420</v>
       </c>
       <c r="B31" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121757019</v>
+        <v>121756964</v>
       </c>
       <c r="B2" t="n">
-        <v>94561</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477273</v>
+        <v>477330</v>
       </c>
       <c r="R2" t="n">
-        <v>6592019</v>
+        <v>6592187</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,42 +777,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756981</v>
+        <v>121756994</v>
       </c>
       <c r="B3" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477298</v>
+        <v>477345</v>
       </c>
       <c r="R3" t="n">
-        <v>6592107</v>
+        <v>6592038</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121757038</v>
+        <v>121757004</v>
       </c>
       <c r="B4" t="n">
-        <v>94561</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477280</v>
+        <v>477319</v>
       </c>
       <c r="R4" t="n">
-        <v>6592050</v>
+        <v>6591993</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,56 +981,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756975</v>
+        <v>129481787</v>
       </c>
       <c r="B5" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477346</v>
+        <v>477295</v>
       </c>
       <c r="R5" t="n">
-        <v>6592119</v>
+        <v>6592173</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,12 +1046,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,34 +1070,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756948</v>
+        <v>129492837</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,40 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477272</v>
+        <v>477205</v>
       </c>
       <c r="R6" t="n">
-        <v>6592291</v>
+        <v>6592083</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,12 +1153,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,34 +1177,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121757004</v>
+        <v>130210236</v>
       </c>
       <c r="B7" t="n">
-        <v>96692</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1223,21 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Karlsdal, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477319</v>
+        <v>477221</v>
       </c>
       <c r="R7" t="n">
-        <v>6591993</v>
+        <v>6592064</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1281,12 +1264,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,34 +1283,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121757025</v>
+        <v>121757019</v>
       </c>
       <c r="B8" t="n">
-        <v>94571</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477277</v>
+        <v>477273</v>
       </c>
       <c r="R8" t="n">
-        <v>6592037</v>
+        <v>6592019</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,15 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121756994</v>
+        <v>121757038</v>
       </c>
       <c r="B9" t="n">
-        <v>96692</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477345</v>
+        <v>477280</v>
       </c>
       <c r="R9" t="n">
-        <v>6592038</v>
+        <v>6592050</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1528,15 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121756964</v>
+        <v>121757025</v>
       </c>
       <c r="B10" t="n">
-        <v>96692</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477330</v>
+        <v>477277</v>
       </c>
       <c r="R10" t="n">
-        <v>6592187</v>
+        <v>6592037</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1635,65 +1607,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121756955</v>
+        <v>129481322</v>
       </c>
       <c r="B11" t="n">
-        <v>56576</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477334</v>
+        <v>477368</v>
       </c>
       <c r="R11" t="n">
-        <v>6592193</v>
+        <v>6592070</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1717,12 +1672,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,27 +1702,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124131732</v>
+        <v>127726928</v>
       </c>
       <c r="B12" t="n">
-        <v>57429</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,44 +1725,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100067</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477347</v>
+        <v>477337</v>
       </c>
       <c r="R12" t="n">
-        <v>6592152</v>
+        <v>6592012</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,22 +1782,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,6 +1806,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1871,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127702435</v>
+        <v>121756948</v>
       </c>
       <c r="B13" t="n">
-        <v>80106</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,37 +1836,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477288</v>
+        <v>477272</v>
       </c>
       <c r="R13" t="n">
-        <v>6592007</v>
+        <v>6592291</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1936,22 +1893,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,82 +1907,64 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127718476</v>
+        <v>127718546</v>
       </c>
       <c r="B14" t="n">
-        <v>57684</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477333</v>
+        <v>477357</v>
       </c>
       <c r="R14" t="n">
-        <v>6592061</v>
+        <v>6591996</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +1996,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,12 +2006,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökande på barksprucken gran.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127718688</v>
+        <v>129481130</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2144,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477357</v>
+        <v>477202</v>
       </c>
       <c r="R15" t="n">
-        <v>6591996</v>
+        <v>6592084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,22 +2098,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127718546</v>
+        <v>129927635</v>
       </c>
       <c r="B16" t="n">
-        <v>91336</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477357</v>
+        <v>477326</v>
       </c>
       <c r="R16" t="n">
-        <v>6591996</v>
+        <v>6592004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,22 +2205,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,48 +2247,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127726928</v>
+        <v>131333420</v>
       </c>
       <c r="B17" t="n">
-        <v>92653</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477337</v>
+        <v>477285</v>
       </c>
       <c r="R17" t="n">
-        <v>6592012</v>
+        <v>6592033</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,22 +2312,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,7 +2336,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2434,59 +2354,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127717234</v>
+        <v>127718688</v>
       </c>
       <c r="B18" t="n">
-        <v>57684</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477214</v>
+        <v>477357</v>
       </c>
       <c r="R18" t="n">
-        <v>6592053</v>
+        <v>6591996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2518,7 +2424,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2528,12 +2434,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringbarkning i tall.</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,59 +2461,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129481200</v>
+        <v>129481925</v>
       </c>
       <c r="B19" t="n">
-        <v>57577</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477304</v>
+        <v>477367</v>
       </c>
       <c r="R19" t="n">
-        <v>6592226</v>
+        <v>6592224</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2644,7 +2531,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2654,12 +2541,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Höstlätet.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,65 +2568,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129482344</v>
+        <v>129481999</v>
       </c>
       <c r="B20" t="n">
-        <v>56917</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477243</v>
+        <v>477369</v>
       </c>
       <c r="R20" t="n">
-        <v>6592288</v>
+        <v>6592224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,7 +2638,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2648,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,32 +2675,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129481322</v>
+        <v>131114362</v>
       </c>
       <c r="B21" t="n">
-        <v>96026</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2810</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477368</v>
+        <v>477396</v>
       </c>
       <c r="R21" t="n">
-        <v>6592070</v>
+        <v>6591981</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,22 +2740,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,32 +2782,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129492837</v>
+        <v>131114635</v>
       </c>
       <c r="B22" t="n">
-        <v>97411</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2817,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477205</v>
+        <v>477372</v>
       </c>
       <c r="R22" t="n">
-        <v>6592083</v>
+        <v>6592200</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,22 +2847,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,32 +2889,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129481130</v>
+        <v>131114655</v>
       </c>
       <c r="B23" t="n">
-        <v>91563</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +2924,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477202</v>
+        <v>477360</v>
       </c>
       <c r="R23" t="n">
-        <v>6592084</v>
+        <v>6592198</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3092,22 +2954,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,32 +2996,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129481787</v>
+        <v>131114771</v>
       </c>
       <c r="B24" t="n">
-        <v>97411</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3169,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477295</v>
+        <v>477355</v>
       </c>
       <c r="R24" t="n">
-        <v>6592173</v>
+        <v>6592214</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3199,22 +3061,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129481249</v>
+        <v>129926849</v>
       </c>
       <c r="B25" t="n">
-        <v>57896</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,48 +3114,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477378</v>
+        <v>477266</v>
       </c>
       <c r="R25" t="n">
-        <v>6592070</v>
+        <v>6592122</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,22 +3168,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,45 +3210,55 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926849</v>
+        <v>124131732</v>
       </c>
       <c r="B26" t="n">
-        <v>78937</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100067</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477266</v>
+        <v>477347</v>
       </c>
       <c r="R26" t="n">
-        <v>6592122</v>
+        <v>6592152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3427,22 +3285,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3469,45 +3327,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129927635</v>
+        <v>127717234</v>
       </c>
       <c r="B27" t="n">
-        <v>91692</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477326</v>
+        <v>477214</v>
       </c>
       <c r="R27" t="n">
-        <v>6592004</v>
+        <v>6592053</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3534,22 +3406,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringbarkning i tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3576,32 +3453,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130210236</v>
+        <v>127718476</v>
       </c>
       <c r="B28" t="n">
-        <v>97578</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3609,19 +3486,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Karlsdal, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477221</v>
+        <v>477333</v>
       </c>
       <c r="R28" t="n">
-        <v>6592064</v>
+        <v>6592061</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3645,17 +3537,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Födosökande på barksprucken gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3670,57 +3572,71 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131114362</v>
+        <v>127702577</v>
       </c>
       <c r="B29" t="n">
-        <v>79254</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477396</v>
+        <v>477362</v>
       </c>
       <c r="R29" t="n">
-        <v>6591981</v>
+        <v>6591979</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3747,22 +3663,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färsk blåbärsspillning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3789,32 +3710,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131333328</v>
+        <v>131332664</v>
       </c>
       <c r="B30" t="n">
-        <v>58063</v>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3827,23 +3748,27 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477310</v>
+        <v>477194</v>
       </c>
       <c r="R30" t="n">
-        <v>6592199</v>
+        <v>6592317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3875,7 +3800,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3885,7 +3810,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Med blindtarmsutfällning -nattgrop.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3912,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131333420</v>
+        <v>121756955</v>
       </c>
       <c r="B31" t="n">
-        <v>91801</v>
+        <v>57132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3923,37 +3853,49 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477285</v>
+        <v>477334</v>
       </c>
       <c r="R31" t="n">
-        <v>6592033</v>
+        <v>6592193</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3977,22 +3919,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4007,22 +3939,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131334799</v>
+        <v>129482344</v>
       </c>
       <c r="B32" t="n">
-        <v>57095</v>
+        <v>57132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,16 +3962,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4049,7 +3981,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4057,21 +3989,27 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477212</v>
+        <v>477243</v>
       </c>
       <c r="R32" t="n">
-        <v>6592292</v>
+        <v>6592288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,27 +4036,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Grop i snötäcket.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4142,6 +4075,1318 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131334799</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>477212</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6592292</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Grop i snötäcket.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129481200</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>477304</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6592226</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Höstlätet.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130307942</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57785</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>477219</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6592318</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Kontakläte hona.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127716629</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>477232</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6592127</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129479912</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>477246</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6592235</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129481249</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>477378</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6592070</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129482751</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>477237</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6592311</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Med andra mesar.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131333328</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>477310</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6592199</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127702435</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>477288</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6592007</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121756975</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>477346</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6592119</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121756981</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>477298</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6592107</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59524-2025 artfynd.xlsx
+++ b/artfynd/A 59524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121756964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121756994</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121757004</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481787</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129492837</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210236</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121757019</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121757038</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121757025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481322</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,6 +1877,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127726928</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1923,6 +1983,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121756948</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127718546</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2137,6 +2207,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481130</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2244,6 +2319,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129927635</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2351,6 +2431,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131333420</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2458,6 +2543,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127718688</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2565,6 +2655,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481925</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2672,6 +2767,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481999</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2779,6 +2879,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131114362</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2886,6 +2991,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131114635</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2993,6 +3103,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131114655</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3100,6 +3215,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131114771</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129926849</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3324,6 +3449,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124131732</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3450,6 +3580,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717234</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3581,6 +3716,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127718476</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3707,6 +3847,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702577</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3839,6 +3984,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131332664</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3948,6 +4098,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121756955</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4075,6 +4230,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482344</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4201,6 +4361,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131334799</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4327,6 +4492,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481200</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4455,6 +4625,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307942</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4576,6 +4751,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127716629</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4702,6 +4882,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129479912</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4823,6 +5008,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129481249</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4955,6 +5145,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129482751</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5078,6 +5273,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131333328</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5185,6 +5385,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702435</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5286,6 +5491,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121756975</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5387,8 +5597,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121756981</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>